--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.79198232341328</v>
+        <v>3.866197127554658</v>
       </c>
       <c r="D2" t="n">
-        <v>23.71805428408882</v>
+        <v>3.854183821164432</v>
       </c>
       <c r="E2" t="n">
-        <v>11.71670925919406</v>
+        <v>1.903965254619035</v>
       </c>
       <c r="F2" t="n">
-        <v>5.188171006877504</v>
+        <v>0.8430777886175942</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.81323581291374</v>
+        <v>8.419650819598482</v>
       </c>
       <c r="D3" t="n">
-        <v>11.05160672261694</v>
+        <v>1.795886092425253</v>
       </c>
       <c r="E3" t="n">
-        <v>11.71670925919406</v>
+        <v>1.903965254619035</v>
       </c>
       <c r="F3" t="n">
-        <v>5.188171006877504</v>
+        <v>0.8430777886175942</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.17594658297183</v>
+        <v>7.016091319732922</v>
       </c>
       <c r="D4" t="n">
-        <v>16.49159905849557</v>
+        <v>2.679884847005531</v>
       </c>
       <c r="E4" t="n">
-        <v>11.71670925919406</v>
+        <v>1.903965254619035</v>
       </c>
       <c r="F4" t="n">
-        <v>5.188171006877504</v>
+        <v>0.8430777886175942</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
